--- a/data/trans_camb/IP19C02-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C02-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>16.85030526506495</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>37.58918001792096</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>18.08407530138027</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>31.66873597702498</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>17.46031028612417</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>34.79146073214371</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>9.675671232868185</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>25.29994719617608</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>10.67496263631465</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>18.03349906058025</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>12.55845267531558</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>25.51320894733448</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>24.36027425739817</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>51.22765037139671</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>24.82673524156815</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>44.19289633734184</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>22.47280803850963</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>43.57884368996268</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>2.910166636245031</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>6.491916665673552</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>3.281812954980557</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>5.747093299778885</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>3.090976759573349</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>6.159088515175328</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>0.9164661435006287</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>2.821338165993721</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1.036188949054336</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>2.368396747343347</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1.543258950739654</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>3.272493293622916</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>7.65984377600062</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>15.97392619771948</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>7.599322440941367</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>15.28833522803655</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>6.100336081387644</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>10.86689790478117</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>11.29799351021646</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>35.55337583300707</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>7.643152163969429</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>28.62612336456936</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>9.489238442483943</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>32.28641089211299</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>4.343453075814018</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>24.95760958829295</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.08216310080766281</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>19.53147698968719</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>4.451502801787267</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>25.03743617304697</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>19.6566784215079</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>46.14962928317361</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>15.35148713157952</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>38.91325999997009</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>14.91531725895461</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>40.23446083697191</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>1.747889840496999</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>5.500391229441766</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.863635439057382</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>3.234599297527413</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1.246835293020282</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>4.242262098190399</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>0.3242332423079244</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>2.582188561046161</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.02385068520522235</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>1.500365584228027</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0.4081363627683147</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>2.342117213760142</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>4.86451659233584</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>11.89014887516331</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>2.896789419149233</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>7.173135164636736</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2.562136620895069</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>7.008918349575853</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>13.1298262835162</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>25.58448681020556</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>14.41914585461748</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>29.90939718879504</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>13.72403726665137</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>27.63568896688208</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>4.428329265299855</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>17.91524356451389</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>7.202423714001635</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>22.34870584327577</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>8.304982043113416</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>22.19933476404787</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>22.534553782718</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>34.08007144009959</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>22.90585492829541</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>38.61379906756077</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>20.31858875228036</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>33.04008590935643</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>1.871023327325727</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>3.645834347378167</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>4.180026395362547</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>8.670560030330059</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>2.591669418831355</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>5.21876825107741</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>0.3075035185913795</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>1.581515359664337</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0.9329537823233252</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>2.709894175707235</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.9922500498742155</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>2.642343688167418</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>5.179715559253655</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>9.703131885698729</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>20.48452665003731</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>35.75372898988339</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>5.546851972841508</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>10.1978447462834</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>7.809578247089694</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>15.06058063400516</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>8.159958658256187</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>17.35834404216126</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>7.975665505851187</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>16.12580059274428</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-1.489373346586421</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>5.87084454881445</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.4807265430701023</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>9.635953294445763</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>1.738427550441723</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>10.44158885273459</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>17.62003724405027</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>23.0791247479105</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>18.10722578831466</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>25.15862578105068</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>15.24196342986152</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>21.91486270049046</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>1.383261750572011</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>2.667586452596001</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>2.712752760722646</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>5.770727241896288</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>1.804093729934412</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>3.647652439561248</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.2828930959889872</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.4337023554092038</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.7225783442913295</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0.7627867643190539</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0.1677415734705534</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>1.210346762174234</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,20 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>8.722728665620256</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>12.54259467379063</v>
+      </c>
       <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
+        <v>8.40764288761361</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>10.92355748799569</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1236,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>13.2625035392803</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>27.38277473825251</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>13.03945928311405</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>26.02191701505163</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>13.14700052335398</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>26.77618716339831</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1262,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>9.061425371352124</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>22.39036738446285</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>8.979093627400076</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>21.3873574601771</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>10.5205591842777</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>23.13306587852851</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1288,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>17.55057735876847</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>32.42497849983739</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>16.8258097010299</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>30.70528609597001</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>16.1153420365665</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>29.95894475834837</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1314,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>2.110625931804902</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>4.357759021602059</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>2.263079105863167</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>4.516265238661394</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>2.180445264064256</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>4.440861654064602</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1340,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>1.078854959217418</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>2.743891070363277</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>1.171080199766641</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>2.742878615625687</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>1.444504313898624</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>3.193701222288987</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1366,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>3.744028156283068</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>7.129837289052471</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>3.853613555442059</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>7.213667279273055</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>3.204610013356104</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>5.962524421998535</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1394,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
